--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -705,17 +705,18 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>금요일 · 가마쿠라
-08:30 신주쿠 출발 목표
-역 주변 → 점심 → 하세 지역
-14:30 가마쿠라 출발, 15:40경 신주쿠</t>
+          <t>금요일 · 가마쿠라 → 요코하마
+07:30 신주쿠 출발(쇼난신주쿠라인 즈시행)
+08:40 대불 또는 하세데라 → 09:50 고마치도리·하치만구
+12:30 요코하마 사쿠라기초 → 13:15 노게 선술집 거리
+14:45 출발, 15:40경 신주쿠</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>10:45 도착 / 11:00 목표
-가마쿠라 아키모토
-시라스·현지 채소</t>
+          <t>11:10 가마쿠라 아키모토
+시라스·현지 채소
+13:15 노게 피오시티 지하 2층(앉는 가게: 메노지·고노고)</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -730,14 +731,14 @@
       <c r="E9" s="15" t="inlineStr">
         <is>
           <t>대불 또는 하세데라 중 1곳
-13:45 앉아서 휴식
-14:30 가마쿠라 출발 목표</t>
+하치만구 본궁 계단(약 60단)이 힘들면 아래에서 참배
+노게에서 앉아서 쉬기</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>생시라스 미입고 → 익힌 시라스
-비·피로 시 하세 지역 축소
+          <t>10/2 오전 비가 많으면 10/3과 낮 일정 교체
+생시라스 미입고 → 익힌 시라스
 신발 재고는 미리 전화(03-5325-0722)
 없으면 도부 이케부쿠로 2F(03-5951-6599)
 저녁 일정은 날짜 고정</t>
@@ -882,7 +883,7 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2일↔3일 교체: 가마쿠라와 서부 도쿄(메이지신궁·마이센·카나데)의 낮 일정만 서로 바꿉니다. 저녁은 날짜 고정: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 10/1 저녁 9~16시 강수·바람 확인.</t>
+          <t>2일↔3일 교체: 가마쿠라·요코하마 노게와 서부 도쿄(메이지신궁·마이센·카나데)의 낮 일정만 서로 바꿉니다. 저녁은 날짜 고정: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 10/1 저녁 9~16시 강수·바람 확인.</t>
         </is>
       </c>
     </row>
@@ -972,19 +973,19 @@
       </c>
       <c r="C19" s="47">
         <f>'맛집 상세'!E7</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="D19" s="47">
         <f>'맛집 상세'!F7</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="E19" s="47">
         <f>C19*$B$17</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="F19" s="47">
         <f>D19*$B$17</f>
-        <v/>
+        <v>6000</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1000,19 +1001,19 @@
       </c>
       <c r="C20" s="47">
         <f>'맛집 상세'!E8</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="D20" s="47">
         <f>'맛집 상세'!F8</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="E20" s="47">
         <f>C20*$B$17</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="F20" s="47">
         <f>D20*$B$17</f>
-        <v/>
+        <v>10500</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1028,19 +1029,19 @@
       </c>
       <c r="C21" s="47">
         <f>'맛집 상세'!E9</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="D21" s="47">
         <f>'맛집 상세'!F9</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="E21" s="47">
         <f>C21*$B$17</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="F21" s="47">
         <f>D21*$B$17</f>
-        <v/>
+        <v>13500</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -1056,19 +1057,19 @@
       </c>
       <c r="C22" s="47">
         <f>'맛집 상세'!E10</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="D22" s="47">
         <f>'맛집 상세'!F10</f>
-        <v/>
+        <v>3500</v>
       </c>
       <c r="E22" s="47">
         <f>C22*$B$17</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="F22" s="47">
         <f>D22*$B$17</f>
-        <v/>
+        <v>10500</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -1084,19 +1085,19 @@
       </c>
       <c r="C23" s="47">
         <f>'맛집 상세'!E13</f>
-        <v/>
+        <v>6500</v>
       </c>
       <c r="D23" s="47">
         <f>'맛집 상세'!F13</f>
-        <v/>
+        <v>8500</v>
       </c>
       <c r="E23" s="47">
         <f>C23*$B$17</f>
-        <v/>
+        <v>19500</v>
       </c>
       <c r="F23" s="47">
         <f>D23*$B$17</f>
-        <v/>
+        <v>25500</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1112,19 +1113,19 @@
       </c>
       <c r="C24" s="47">
         <f>'맛집 상세'!E12</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="D24" s="47">
         <f>'맛집 상세'!F12</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="E24" s="47">
         <f>C24*$B$17</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="F24" s="47">
         <f>D24*$B$17</f>
-        <v/>
+        <v>7500</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1140,19 +1141,19 @@
       </c>
       <c r="C25" s="47">
         <f>'맛집 상세'!E11</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D25" s="47">
         <f>'맛집 상세'!F11</f>
-        <v/>
+        <v>14000</v>
       </c>
       <c r="E25" s="47">
         <f>C25*$B$17</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="F25" s="47">
         <f>D25*$B$17</f>
-        <v/>
+        <v>42000</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -1174,11 +1175,11 @@
       </c>
       <c r="E26" s="47">
         <f>C26*$B$17</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="F26" s="47">
         <f>D26*$B$17</f>
-        <v/>
+        <v>6000</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -1194,19 +1195,19 @@
       </c>
       <c r="C27" s="47">
         <f>$D$17*$F$17</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="D27" s="47">
         <f>$D$17*$F$17</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="E27" s="47">
         <f>C27*$B$17</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="F27" s="47">
         <f>D27*$B$17</f>
-        <v/>
+        <v>12000</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -1222,19 +1223,19 @@
       </c>
       <c r="C28" s="47">
         <f>'맛집 상세'!E23</f>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="D28" s="47">
         <f>'맛집 상세'!F23</f>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="E28" s="47">
         <f>C28*$B$17</f>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="F28" s="47">
         <f>D28*$B$17</f>
-        <v/>
+        <v>12600</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -1274,45 +1275,45 @@
       </c>
       <c r="C30" s="47">
         <f>'맛집 상세'!E24</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="D30" s="47">
         <f>'맛집 상세'!F24</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="E30" s="47">
         <f>C30*$B$17</f>
-        <v/>
+        <v>2700</v>
       </c>
       <c r="F30" s="47">
         <f>D30*$B$17</f>
-        <v/>
+        <v>4500</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>추가 간식</t>
+          <t>추가 간식·노게</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>위 카페 외 여행 전체 여유액</t>
+          <t>노게 선술집(1,500~3,000) + 여행 전체 간식 여유</t>
         </is>
       </c>
       <c r="C31" s="47" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="D31" s="47" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E31" s="47">
         <f>C31*$B$17</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="F31" s="47">
         <f>D31*$B$17</f>
-        <v/>
+        <v>15000</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
@@ -1328,19 +1329,19 @@
       </c>
       <c r="C32" s="48">
         <f>SUM(C19:C31)</f>
-        <v/>
+        <v>39500</v>
       </c>
       <c r="D32" s="48">
         <f>SUM(D19:D31)</f>
-        <v/>
+        <v>55200</v>
       </c>
       <c r="E32" s="48">
         <f>SUM(E19:E31)</f>
-        <v/>
+        <v>118500</v>
       </c>
       <c r="F32" s="48">
         <f>SUM(F19:F31)</f>
-        <v/>
+        <v>165600</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -1394,11 +1395,11 @@
       </c>
       <c r="E35" s="47">
         <f>C35*$B$17</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F35" s="47">
         <f>D35*$B$17</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
@@ -1414,19 +1415,19 @@
       </c>
       <c r="C36" s="48">
         <f>SUM(C34:C35)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="D36" s="48">
         <f>SUM(D34:D35)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="E36" s="48">
         <f>SUM(E34:E35)</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="F36" s="48">
         <f>SUM(F34:F35)</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
@@ -1442,19 +1443,19 @@
       </c>
       <c r="C37" s="48">
         <f>C32+C36</f>
-        <v/>
+        <v>39800</v>
       </c>
       <c r="D37" s="48">
         <f>D32+D36</f>
-        <v/>
+        <v>55500</v>
       </c>
       <c r="E37" s="48">
         <f>E32+E36</f>
-        <v/>
+        <v>119400</v>
       </c>
       <c r="F37" s="48">
         <f>F32+F36</f>
-        <v/>
+        <v>166500</v>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
@@ -2681,7 +2682,7 @@
       <c r="B18" s="36" t="inlineStr">
         <is>
           <t>대안
-10/3 저녁</t>
+10/4 저녁 (폰가 대신)</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
@@ -2695,7 +2696,7 @@
       <c r="D18" s="15" t="inlineStr">
         <is>
           <t>니기리 모둠·계절 스시
-폰가 예산이 부담스럽거나 고기보다 스시를 원할 때 대체. 폰가와 둘 다 가지 않음.</t>
+폰가 예약이 안 되거나 고기보다 스시를 원할 때 10/4 저녁 대체.</t>
         </is>
       </c>
       <c r="E18" s="50" t="n">
@@ -2712,7 +2713,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>폰가 대신 선택하면 에비스 쇼핑을 빼고 카나데 이후 시부야로 이동. 두 저녁을 함께 예약하지 않음. 토요일에 평일 전용 원격 대기를 사용할 수 있다고 가정하지 않음.</t>
+          <t>폰가 예약이 안 될 때 에비스 그릇 가게 뒤 JR로 시부야까지 1정거장. 긴자 라이온과 둘 중 하나만 고르고 두 곳을 함께 예약하지 않음.</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -3157,7 +3158,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>13세 미만 입장 불가 안내. 일반 카페는 예약 불가. 네즈·카나데 대신 14:00 방문 후 에비스로 이동. 세 카페를 모두 넣지 않음. 서비스료 없음.</t>
+          <t>13세 미만 입장 불가 안내. 일반 카페는 예약 불가. 네즈·카나데 대신 14:00 방문 후 하쓰다이(우나후지)로 이동. 세 카페를 모두 넣지 않음. 서비스료 없음.</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -618,7 +618,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>하루 주 카페 1곳. 서부 일정일은 카나데 14:00~15:30, 네즈·사샤는 교체 후보입니다. 일요일 하마리큐 다실은 날씨·체력에 따라 선택. 카페 6곳을 모두 가는 일정이 아닙니다.</t>
+          <t>하루 주 카페 1곳. 서부 일정일은 카나데 14:00~15:30, 네즈·사샤는 교체 후보입니다. 하마리큐 다실·사후는 10/4가 요코하마 저녁으로 바뀌어 이번에는 넣지 않았습니다.</t>
         </is>
       </c>
     </row>
@@ -705,18 +705,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>금요일 · 가마쿠라 → 요코하마
+          <t>금요일 · 가마쿠라 (아침 일찍)
 07:30 신주쿠 출발(쇼난신주쿠라인 즈시행)
 08:40 대불 또는 하세데라 → 09:50 고마치도리·하치만구
-12:30 요코하마 사쿠라기초 → 13:15 노게 선술집 거리
-14:45 출발, 15:40경 신주쿠</t>
+12:30 가마쿠라 출발 → 13:45 숙소에서 쉬기
+15:40 숙소 출발</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
           <t>11:10 가마쿠라 아키모토
-시라스·현지 채소
-13:15 노게 피오시티 지하 2층(앉는 가게: 메노지·고노고)</t>
+시라스·현지 채소</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -730,9 +729,9 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>대불 또는 하세데라 중 1곳
+          <t>대불 또는 하세데라 중 1곳(다리가 괜찮으면 둘 다)
 하치만구 본궁 계단(약 60단)이 힘들면 아래에서 참배
-노게에서 앉아서 쉬기</t>
+13:45~15:30 숙소 휴식</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -794,42 +793,40 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>일요일 · 동부 도쿄
-09:30 아사쿠사
-12:30 아키하바라 가이요도 하비로비 도쿄
-(라디오회관 5F · 토일 11:00~19:00)
-하마리큐(선택) → 긴자 → 에비스</t>
+          <t>일요일 · 아사쿠사 → 요코하마의 밤
+09:30 아사쿠사 → 12:30 아키하바라 가이요도 하비로비
+13:30 숙소에서 쉬기 → 15:45 요코하마로
+16:45 에어 캐빈(해 지는 시각 17:23)</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
           <t>11:00 나미키 야부소바
 소바·튀김
-저녁 야키니쿠를 위해 가볍게</t>
+저녁 노게를 위해 가볍게</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>18:00 폰가 에비스
-미예약 · 3명 예약 필요
-안 되면 긴자 비어홀 라이온 7초메
-(일 11:30~22:00)</t>
+          <t>18:00 요코하마 노게 저녁
+노게노 다이도코로 파오시티(97석, 일 12~23시)
+핫페퍼 예약 권장 · 안 되면 피오시티 지하 2층
+19:45 출발, 21:00경 숙소</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>13:45~15:00 하마리큐·오차야(선택)
-15:15 긴자 짧게
-16:30 히비야선으로 에비스
-16:50 에비스 그릇 1곳(선택)</t>
+          <t>13:30~15:30 숙소 휴식
+에어 캐빈 왕복 1,800엔(성인)
+운하파크에서 미나토미라이 야경</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>비·보행 부담 시 하마리큐 제외
-아키하바라 가게는 실내라 그대로
-피곤하면 에비스 그릇 생략
-19:45 택시로 숙소</t>
+          <t>아키하바라 가게는 실내라 비가 와도 그대로
+강풍으로 에어 캐빈이 멈추면 역 앞에서 야경만
+피곤하면 요코하마를 빼고 숙소 근처에서 저녁
+폰가·에비스·긴자는 이번 일정에서 제외</t>
         </is>
       </c>
     </row>
@@ -883,7 +880,7 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2일↔3일 교체: 가마쿠라·요코하마 노게와 서부 도쿄(메이지신궁·마이센·카나데)의 낮 일정만 서로 바꿉니다. 저녁은 날짜 고정: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 10/1 저녁 9~16시 강수·바람 확인.</t>
+          <t>2일↔3일 교체: 가마쿠라와 서부 도쿄(메이지신궁·마이센·카나데)의 낮 일정만 서로 바꿉니다. 저녁은 날짜 고정: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 요코하마는 10/4 저녁.</t>
         </is>
       </c>
     </row>
@@ -1136,24 +1133,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>야키니쿠 폰가 에비스 (예약 필요)</t>
-        </is>
-      </c>
-      <c r="C25" s="47">
-        <f>'맛집 상세'!E11</f>
-        <v>12000</v>
-      </c>
-      <c r="D25" s="47">
-        <f>'맛집 상세'!F11</f>
-        <v>14000</v>
+          <t>요코하마 노게 저녁 (파오시티 등, 예약 권장)</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D25" s="47" t="n">
+        <v>5000</v>
       </c>
       <c r="E25" s="47">
         <f>C25*$B$17</f>
-        <v>36000</v>
+        <v>9000</v>
       </c>
       <c r="F25" s="47">
         <f>D25*$B$17</f>
-        <v>42000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -1270,50 +1265,48 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>나카지마노 오차야</t>
-        </is>
-      </c>
-      <c r="C30" s="47">
-        <f>'맛집 상세'!E24</f>
-        <v>900</v>
-      </c>
-      <c r="D30" s="47">
-        <f>'맛집 상세'!F24</f>
-        <v>1500</v>
+          <t>나카지마노 오차야 (이번 일정 제외)</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="47" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="47">
         <f>C30*$B$17</f>
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="F30" s="47">
         <f>D30*$B$17</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>추가 간식·노게</t>
+          <t>추가 간식</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>노게 선술집(1,500~3,000) + 여행 전체 간식 여유</t>
+          <t>위 카페 외 여행 전체 여유액</t>
         </is>
       </c>
       <c r="C31" s="47" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="D31" s="47" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E31" s="47">
         <f>C31*$B$17</f>
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="F31" s="47">
         <f>D31*$B$17</f>
-        <v>15000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
@@ -1329,19 +1322,19 @@
       </c>
       <c r="C32" s="48">
         <f>SUM(C19:C31)</f>
-        <v>39500</v>
+        <v>28100</v>
       </c>
       <c r="D32" s="48">
         <f>SUM(D19:D31)</f>
-        <v>55200</v>
+        <v>41700</v>
       </c>
       <c r="E32" s="48">
         <f>SUM(E19:E31)</f>
-        <v>118500</v>
+        <v>84300</v>
       </c>
       <c r="F32" s="48">
         <f>SUM(F19:F31)</f>
-        <v>165600</v>
+        <v>125100</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -1384,22 +1377,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>하마리큐 / 성인 일반</t>
+          <t>요코하마 에어 캐빈 왕복 / 성인</t>
         </is>
       </c>
       <c r="C35" s="47" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="D35" s="47" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="E35" s="47">
         <f>C35*$B$17</f>
-        <v>900</v>
+        <v>5400</v>
       </c>
       <c r="F35" s="47">
         <f>D35*$B$17</f>
-        <v>900</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
@@ -1410,24 +1403,24 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>선택 방문 하마리큐만</t>
+          <t>에어 캐빈 왕복만(대불·하세데라 입장료 별도)</t>
         </is>
       </c>
       <c r="C36" s="48">
         <f>SUM(C34:C35)</f>
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="D36" s="48">
         <f>SUM(D34:D35)</f>
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="E36" s="48">
         <f>SUM(E34:E35)</f>
-        <v>900</v>
+        <v>5400</v>
       </c>
       <c r="F36" s="48">
         <f>SUM(F34:F35)</f>
-        <v>900</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
@@ -1443,25 +1436,25 @@
       </c>
       <c r="C37" s="48">
         <f>C32+C36</f>
-        <v>39800</v>
+        <v>29900</v>
       </c>
       <c r="D37" s="48">
         <f>D32+D36</f>
-        <v>55500</v>
+        <v>43500</v>
       </c>
       <c r="E37" s="48">
         <f>E32+E36</f>
-        <v>119400</v>
+        <v>89700</v>
       </c>
       <c r="F37" s="48">
         <f>F32+F36</f>
-        <v>166500</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>카나데는 세금·서비스 15% 포함, 폰가는 서비스 10% 별도. 네즈 선택 시 카나데를 빼고 네즈 음료 800~1,700엔+입장 1,400엔/인을 더합니다. 총계는 항공·숙박·교통·쇼핑·기타 관광 입장료 제외.</t>
+          <t>카나데는 세금·서비스 15% 포함. 네즈 선택 시 카나데를 빼고 네즈 음료 800~1,700엔+입장 1,400엔/인을 더합니다. 총계는 항공·숙박·교통·쇼핑·기타 관광 입장료(대불 300엔·하세데라 400엔 등) 제외.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1545,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>폰가 에비스</t>
+          <t>노게노 다이도코로 파오시티</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1562,17 +1555,17 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>코스 총액·메뉴 대체·엘리베이터</t>
+          <t>성인 3명 테이블 · 핫페퍼 온라인 예약</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>미예약·빈자리 미확인</t>
+          <t>미예약 · 예약 권장</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>10% 서비스료 포함 총액 확인. 생고기·내장 제외 요청 수용 여부 확인. 예약이 안 되면 긴자 라이온 7초메로.</t>
+          <t>일요일 저녁이라 붐빌 수 있음. 안 되면 사쿠라기초역과 바로 이어진 피오시티 지하 2층 선술집 거리에서 빈자리.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1796,7 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>일본식 다실 경험: 나카지마노 오차야. 맑은 날 하마리큐 산책과 묶습니다. 비 오면 사후 또는 긴자 시세이도 중 한 곳으로 바꾸고 둘 다 넣지 않습니다.</t>
+          <t>일본식 다실 경험: 나카지마노 오차야(하마리큐). 10/4가 요코하마 저녁으로 바뀌어 이번 일정에는 넣지 않았습니다. 다음 기회 후보.</t>
         </is>
       </c>
     </row>
@@ -2245,8 +2238,8 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>일정
-10/4 저녁</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C11" s="29" t="inlineStr">
@@ -2325,7 +2318,7 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>자루소바 또는 덴푸라 소바
-저녁 야키니쿠를 고려해 가벼운 점심으로 선택. 타베로그 소바 EAST 백명점 2025 선정 확인.</t>
+저녁 노게를 고려해 가벼운 점심으로 선택. 타베로그 소바 EAST 백명점 2025 선정 확인.</t>
         </is>
       </c>
       <c r="E12" s="50" t="n">
@@ -2558,8 +2551,8 @@
       </c>
       <c r="B16" s="36" t="inlineStr">
         <is>
-          <t>대안 카페
-10/4</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
@@ -2681,8 +2674,8 @@
       </c>
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>대안
-10/4 저녁 (폰가 대신)</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
@@ -2804,8 +2797,8 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>대안 간식
-10/4</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
@@ -3061,8 +3054,8 @@
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>선택 카페
-10/4 맑을 때</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
@@ -3255,8 +3248,8 @@
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>우천 대안
-10/4</t>
+          <t>보류
+이번 일정 제외</t>
         </is>
       </c>
       <c r="C27" s="29" t="inlineStr">

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -837,8 +837,9 @@
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>월요일 · 귀국
-숙소 아침 → 체크아웃
-신주쿠역에서 공항 이동</t>
+09:30 짐 정리·체크아웃 준비
+10:20 숙소 출발(택시) → 신주쿠역
+11:08 N'EX 21호 → 공항제2빌딩 12:27</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -862,10 +863,10 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>11시대 NEX 후보: 실제 열차 확인
-나리타 T3 13:00~13:20 도착 목표
-기존 가이드 16:20 출발 기준
-항공권·터미널은 예약 내역 재확인</t>
+          <t>N'EX 21호(신주쿠 11:08 → 공항제2빌딩 12:27, 평일 시각)
+대안: 11:38 발 23호(12:54) · 10:38 발 19호(11:53)
+제3터미널은 역에서 걸어서 약 15분, 12:45경 도착
+ZE610 16:20 · 10/5는 한국 대체공휴일이라 붐빔</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1679,22 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>출발 전</t>
+          <t>10/1 교환 때</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>편명·터미널·NEX 지정석</t>
+          <t>10/5 N'EX 21호(신주쿠 11:08) 3명 지정석</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>기존 가이드 기준, 재확인 필요</t>
+          <t>바우처 교환 시 지정</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>NEX 11시대는 계획용 구간이지 발권 완료 열차가 아님.</t>
+          <t>지정석 표의 시각이 우선. 21호가 안 되면 23호(11:38) 또는 19호(10:38).</t>
         </is>
       </c>
     </row>

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -681,8 +681,9 @@
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>20:15 이후 목표
-하야시다 신주쿠 본점
-입국·체크인 후 결정</t>
+고기 저녁(신주쿠산초메)
+① 야키니쿠 우시고로 (L.O. 22:30, 03-3358-4129)
+② 에이징 비프 (L.O. 22:00, 03-6273-2985)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -693,9 +694,9 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>라멘 대기 20분 이상 → 교자노 후쿠호
-너무 늦으면 편의점·포장 식사
-진로쿠는 저녁 영업 상충으로 보류</t>
+          <t>3명 예산 10~15만 원(약 11,400~17,400엔)
+코스는 상한을 넘으니 단품 위주
+늦거나 피곤하면 하야시다 라멘</t>
         </is>
       </c>
     </row>
@@ -966,24 +967,22 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>라멘 하야시다 신주쿠 본점</t>
-        </is>
-      </c>
-      <c r="C19" s="47">
-        <f>'맛집 상세'!E7</f>
-        <v>1500</v>
-      </c>
-      <c r="D19" s="47">
-        <f>'맛집 상세'!F7</f>
-        <v>2000</v>
+          <t>고기 저녁 (우시고로 또는 에이징 비프, 3명 10~15만 원)</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D19" s="47" t="n">
+        <v>5800</v>
       </c>
       <c r="E19" s="47">
         <f>C19*$B$17</f>
-        <v>4500</v>
+        <v>11400</v>
       </c>
       <c r="F19" s="47">
         <f>D19*$B$17</f>
-        <v>6000</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1323,19 +1322,19 @@
       </c>
       <c r="C32" s="48">
         <f>SUM(C19:C31)</f>
-        <v>28100</v>
+        <v>30400</v>
       </c>
       <c r="D32" s="48">
         <f>SUM(D19:D31)</f>
-        <v>41700</v>
+        <v>45500</v>
       </c>
       <c r="E32" s="48">
         <f>SUM(E19:E31)</f>
-        <v>84300</v>
+        <v>91200</v>
       </c>
       <c r="F32" s="48">
         <f>SUM(F19:F31)</f>
-        <v>125100</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -1437,19 +1436,19 @@
       </c>
       <c r="C37" s="48">
         <f>C32+C36</f>
-        <v>29900</v>
+        <v>32200</v>
       </c>
       <c r="D37" s="48">
         <f>D32+D36</f>
-        <v>43500</v>
+        <v>47300</v>
       </c>
       <c r="E37" s="48">
         <f>E32+E36</f>
-        <v>89700</v>
+        <v>96600</v>
       </c>
       <c r="F37" s="48">
         <f>F32+F36</f>
-        <v>130500</v>
+        <v>141900</v>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -694,8 +694,8 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>3명 예산 10~15만 원(약 11,400~17,400엔)
-코스는 상한을 넘으니 단품 위주
+          <t>가족 목표 3명 10~15만 원(약 11,400~17,400엔)
+단품 약 15,000엔 · 코스+음료 약 21,000엔
 늦거나 피곤하면 하야시다 라멘</t>
         </is>
       </c>
@@ -967,22 +967,24 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>고기 저녁 (우시고로 또는 에이징 비프, 3명 10~15만 원)</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="n">
-        <v>3800</v>
-      </c>
-      <c r="D19" s="47" t="n">
-        <v>5800</v>
+          <t>고기 저녁 (우시고로 또는 에이징 비프)</t>
+        </is>
+      </c>
+      <c r="C19" s="47">
+        <f>'맛집 상세'!E7</f>
+        <v>5000</v>
+      </c>
+      <c r="D19" s="47">
+        <f>'맛집 상세'!F7</f>
+        <v>7000</v>
       </c>
       <c r="E19" s="47">
         <f>C19*$B$17</f>
-        <v>11400</v>
+        <v>15000</v>
       </c>
       <c r="F19" s="47">
         <f>D19*$B$17</f>
-        <v>17400</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1322,19 +1324,19 @@
       </c>
       <c r="C32" s="48">
         <f>SUM(C19:C31)</f>
-        <v>30400</v>
+        <v>31600</v>
       </c>
       <c r="D32" s="48">
         <f>SUM(D19:D31)</f>
-        <v>45500</v>
+        <v>46700</v>
       </c>
       <c r="E32" s="48">
         <f>SUM(E19:E31)</f>
-        <v>91200</v>
+        <v>94800</v>
       </c>
       <c r="F32" s="48">
         <f>SUM(F19:F31)</f>
-        <v>136500</v>
+        <v>140100</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -1436,19 +1438,19 @@
       </c>
       <c r="C37" s="48">
         <f>C32+C36</f>
-        <v>32200</v>
+        <v>33400</v>
       </c>
       <c r="D37" s="48">
         <f>D32+D36</f>
-        <v>47300</v>
+        <v>48500</v>
       </c>
       <c r="E37" s="48">
         <f>E32+E36</f>
-        <v>96600</v>
+        <v>100200</v>
       </c>
       <c r="F37" s="48">
         <f>F32+F36</f>
-        <v>141900</v>
+        <v>145500</v>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
@@ -1998,39 +2000,41 @@
       </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>라멘 하야시다 신주쿠 본점
-らぁ麺 はやし田 新宿本店
-新宿3-31-5 ペガサス館102
-TEL 03-6380-0047</t>
+          <t>야키니쿠 우시고로 신주쿠산초메점
+焼肉うしごろ 新宿三丁目店
+新宿3-17-10 HULIC &amp;New SHINJUKU 12F
+TEL 03-3358-4129
+(대안) 에이징 비프 TOKYO 신주쿠산초메점
+新宿3-5-4 6F · TEL 03-6273-2985</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>간장 라멘
-오리와 닭을 쓰는 육수가 특징. 도착일에 무거운 코스 대신 한 그릇으로 마무리.</t>
+          <t>흑우 혀(구로탄)·하라미 · 타베로그 3.67, 야키니쿠 백명점 2025
+단품 예시(3명): 혀 1,600×2 + 하라미 2,200×2 + 우치모모 1,800×2 + 김치 모둠 880 = 약 12,100엔, 밥·음료 포함 약 15,000엔</t>
         </is>
       </c>
       <c r="E7" s="49" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="49" t="n">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>매일 11:00~23:00
-20:15 이후 도착 상황에 맞춰 방문. 예약 식사로 묶지 않음.</t>
+          <t>우시고로 17:00~23:30 (L.O. 22:30)
+에이징 비프 17:00~23:00 (L.O. 22:00)
+예약 완료 아님 · N’EX 안에서 전화로 확인</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>예상 대기가 20분을 넘으면 교자노 후쿠호로 전환. 입국·수하물 지연 시 맛집보다 체크인과 휴식 우선.</t>
+          <t>가족 목표 3명 10~15만 원(약 11,400~17,400엔). 코스(1인 6,100엔~, 3명 18,300엔)와 에이징 비프(1인 평균 약 6,200엔)는 상한을 조금 넘음. 메뉴판 가격에 세금·서비스료가 따로 붙을 수 있음. 늦거나 피곤하면 하야시다 라멘(1인 1,500~2,000엔, 新宿3-31-5).</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>원본 #136 / 143행
-영업시간·육수: 운영사 공식</t>
+          <t>공식 매장 페이지 · 타베로그 · 一休 코스 · 메뉴 가격 (10/1 확인)</t>
         </is>
       </c>
       <c r="J7" s="31" t="inlineStr">
@@ -2625,7 +2629,7 @@
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>군만두·물만두·밥
-라멘 대기가 길거나 부모님이 만두를 선호할 때. 마늘 없는 교자 선택 가능.</t>
+고기 저녁 자리가 없거나 부모님이 만두를 선호할 때. 마늘 없는 교자 선택 가능.</t>
         </is>
       </c>
       <c r="E17" s="49" t="n">
@@ -2893,7 +2897,7 @@
       </c>
       <c r="H21" s="40" t="inlineStr">
         <is>
-          <t>이름이 같은 다른 지점으로 바꾸지 않음. 10/1 저녁 이용 가능 여부를 확인한 경우에만 하야시다와 교체.</t>
+          <t>이름이 같은 다른 지점으로 바꾸지 않음. 10/1 저녁 이용 가능 여부를 확인한 경우에만 고기 저녁 대신 고려.</t>
         </is>
       </c>
       <c r="I21" s="40" t="inlineStr">

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="J7" s="31" t="inlineStr">
         <is>
-          <t>원본 지도</t>
+          <t>지도 검색</t>
         </is>
       </c>
       <c r="K7" s="31" t="inlineStr">
@@ -2047,7 +2047,11 @@
           <t>출처 보기</t>
         </is>
       </c>
-      <c r="L7" s="31" t="n"/>
+      <c r="L7" s="35" t="inlineStr">
+        <is>
+          <t>대조 보기</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="142" customHeight="1">
       <c r="A8" s="15" t="n">
@@ -3401,69 +3405,70 @@
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" display="원본 지도" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" display="출처 보기" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" display="지도 검색" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" display="출처 보기" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" display="대조 보기" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" display="지도 검색" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" display="출처 보기" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" display="원본 지도" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" display="출처 보기" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" display="대조 보기" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" display="원본 지도" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" display="출처 보기" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" display="지도 검색" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" display="출처 보기" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" display="대조 보기" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" display="원본 지도" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" display="출처 보기" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" display="대조 보기" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" display="원본 지도" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" display="출처 보기" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" display="지도 검색" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" display="출처 보기" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" display="원본 지도" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" display="출처 보기" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" display="대조 보기" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" display="지도 검색" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" display="출처 보기" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" display="원본 지도" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" display="출처 보기" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" display="대조 보기" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" display="원본 지도" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" display="출처 보기" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" display="대조 보기" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" display="원본 지도" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" display="출처 보기" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" display="대조 보기" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" display="지도 검색" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" display="출처 보기" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" display="대조 보기" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" display="지도 검색" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" display="출처 보기" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" display="대조 보기" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" display="지도 검색" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" display="출처 보기" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" display="대조 보기" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" display="지도 검색" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" display="출처 보기" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" display="대조 보기" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" display="지도 검색" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" display="출처 보기" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" display="대조 보기" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" display="지도 검색" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" display="출처 보기" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" display="대조 보기" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" display="메뉴 PDF" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" display="행사 일정" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" display="지도 검색" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" display="출처 보기" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" display="대조 보기" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" display="지도 검색" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" display="출처 보기" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" display="원본 지도" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" display="출처 보기" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" display="대조 보기" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" display="원본 지도" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" display="출처 보기" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" display="지도 검색" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" display="출처 보기" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" display="대조 보기" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" display="원본 지도" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" display="출처 보기" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" display="대조 보기" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" display="원본 지도" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" display="출처 보기" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" display="지도 검색" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" display="출처 보기" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" display="원본 지도" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" display="출처 보기" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" display="대조 보기" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" display="지도 검색" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" display="출처 보기" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" display="원본 지도" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" display="출처 보기" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" display="대조 보기" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" display="원본 지도" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" display="출처 보기" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" display="대조 보기" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" display="원본 지도" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" display="출처 보기" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" display="대조 보기" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" display="지도 검색" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" display="출처 보기" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" display="대조 보기" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" display="지도 검색" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" display="출처 보기" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" display="대조 보기" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" display="지도 검색" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" display="출처 보기" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" display="대조 보기" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" display="지도 검색" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" display="출처 보기" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" display="대조 보기" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" display="지도 검색" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" display="출처 보기" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" display="대조 보기" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" display="지도 검색" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" display="출처 보기" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" display="대조 보기" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" display="메뉴 PDF" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" display="행사 일정" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId60"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61"/>
   </tableParts>
 </worksheet>
 </file>
--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -597,14 +597,14 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026.10.01(목)~10.05(월) · 성인 3명 기준 · 확인일 2026.09.27 · 10/1 수정 · 시부야 스카이 제외</t>
+          <t>2026.10.01(목)~10.05(월) · 성인 3명 기준 · 확인일 2026.09.27 · 10/2 수정 · 시부야 스카이 제외</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>10/1 수정안: 시각은 목표입니다. 확정 예약은 우나후지 10/3(토) 17:00 한 곳. 기본은 10/2 가마쿠라이며, 날씨에 따라 2·3일의 낮 일정만 교체하고 저녁(10/2 신발·이른 저녁, 10/3 우나후지)은 날짜 그대로 둡니다.</t>
+          <t>10/2 수정안: 시각은 목표입니다. 확정 예약은 우나후지 10/3(토) 17:00 한 곳. 10/2 비로 가마쿠라는 10/3(토) 아침으로 확정했고, 10/2는 에비스 그릇 가게와 엄마 신발 쇼핑입니다. 저녁(10/2 신발·츠나하치, 10/3 우나후지)은 그대로입니다.</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>하루 주 카페 1곳. 서부 일정일은 카나데 14:00~15:30, 네즈·사샤는 교체 후보입니다. 하마리큐 다실·사후는 10/4가 요코하마 저녁으로 바뀌어 이번에는 넣지 않았습니다.</t>
+          <t>카페는 이번 일정에서 선택입니다. 카나데(메구로, 에비스에서 JR 한 정거장)는 쉬어 가고 싶을 때만, 네즈·사샤는 교체 후보입니다. 하마리큐 다실·사후는 10/4가 요코하마 저녁으로 바뀌어 넣지 않았습니다.</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,18 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>금요일 · 가마쿠라 (아침 일찍)
-07:30 신주쿠 출발(쇼난신주쿠라인 즈시행)
-08:40 대불 또는 하세데라 → 09:50 고마치도리·하치만구
-12:30 가마쿠라 출발 → 13:45 숙소에서 쉬기
-15:40 숙소 출발</t>
+          <t>금요일 · 비 오는 날 쇼핑 (가마쿠라는 10/3으로)
+11:00 마이센 아오야마 점심
+12:30 택시로 에비스(약 10분)
+12:45 EAST table 에비스점(미노야키 그릇)
+13:45 THE HARVEST KITCHEN GENERAL STORE
+14:45 숙소에 짐 두고 쉬기 → 15:40 출발</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>11:10 가마쿠라 아키모토
-시라스·현지 채소</t>
+          <t>11:00 마이센 아오야마 본점
+돈가스 정식</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -730,18 +731,19 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>대불 또는 하세데라 중 1곳(다리가 괜찮으면 둘 다)
-하치만구 본궁 계단(약 60단)이 힘들면 아래에서 참배
-13:45~15:30 숙소 휴식</t>
+          <t>그릇 가게 두 곳: 11:00~20:00 / 11:00~19:00, 정기 휴무 없음
+여권 지참(면세 가능 여부는 계산 때 확인)
+그릇은 옷으로 감싸 기내 가방에
+14:45~15:40 숙소 휴식</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>10/2 오전 비가 많으면 10/3과 낮 일정 교체
-생시라스 미입고 → 익힌 시라스
+          <t>비가 세면 가게 사이도 택시로
+피곤하면 THE HARVEST 생략
 신발 재고는 미리 전화(03-5325-0722)
 없으면 도부 이케부쿠로 2F(03-5951-6599)
-저녁 일정은 날짜 고정</t>
+저녁 일정은 그대로</t>
         </is>
       </c>
     </row>
@@ -751,17 +753,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>토요일 · 서부 도쿄
-09:00 메이지신궁 짧게
-오모테산도 → 메구로(카나데) → 하쓰다이
-16:00 하쓰다이로 이동</t>
+          <t>토요일 · 가마쿠라 (아침 일찍, 10/2 비로 옮김)
+07:00 숙소 출발 → 07:30 신주쿠(쇼난신주쿠라인 즈시행)
+08:40 대불 또는 하세데라 → 09:50 고마치도리·하치만구
+12:30 가마쿠라 출발 → 13:45 숙소에서 쉬기
+15:40 숙소 출발 → 16:00 하쓰다이</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>10:45 도착 / 11:00 목표
-마이센 아오야마 본점
-돈가스 정식</t>
+          <t>11:10 가마쿠라 아키모토
+시라스·현지 채소</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -774,17 +776,17 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>14:00~15:30 카나데 라운지
-네즈·사샤는 카나데 대체 후보
-기본안에 두 카페를 더하지 않음</t>
+          <t>대불 또는 하세데라 중 1곳(다리가 괜찮으면 둘 다)
+하치만구 본궁 계단(약 60단)이 힘들면 아래에서 참배
+13:45~15:40 숙소 휴식</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>비·피로 시 메이지신궁 생략
-가마쿠라 10/3 선택 시 낮 일정만 10/2로
-우나후지 17:00은 10/3 그대로
-카나데 예약은 변경 가능 여부 확인</t>
+          <t>토요일이라 붐비니 07:00 출발을 지킴
+생시라스 미입고 → 익힌 시라스
+비가 오면 대불 한 곳만 보고 점심 뒤 귀가
+우나후지 17:00은 그대로</t>
         </is>
       </c>
     </row>
@@ -882,7 +884,7 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2일↔3일 교체: 가마쿠라와 서부 도쿄(메이지신궁·마이센·카나데)의 낮 일정만 서로 바꿉니다. 저녁은 날짜 고정: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 요코하마는 10/4 저녁.</t>
+          <t>날짜 확정(10/2 아침): 비 때문에 가마쿠라를 10/3(토)로 옮기고 10/2를 쇼핑 날로 바꿨습니다. 저녁은 그대로: 10/2 엄마 신발(오다큐)·츠나하치·개인 약속, 10/3 우나후지 17:00 예약. 요코하마는 10/4 저녁.</t>
         </is>
       </c>
     </row>
@@ -995,15 +997,15 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>가마쿠라 아키모토</t>
+          <t>마이센 아오야마 본점 (쇼핑 날)</t>
         </is>
       </c>
       <c r="C20" s="47">
-        <f>'맛집 상세'!E8</f>
+        <f>'맛집 상세'!E10</f>
         <v>2500</v>
       </c>
       <c r="D20" s="47">
-        <f>'맛집 상세'!F8</f>
+        <f>'맛집 상세'!F10</f>
         <v>3500</v>
       </c>
       <c r="E20" s="47">
@@ -1051,15 +1053,15 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>마이센 아오야마 본점</t>
+          <t>가마쿠라 아키모토</t>
         </is>
       </c>
       <c r="C22" s="47">
-        <f>'맛집 상세'!E10</f>
+        <f>'맛집 상세'!E8</f>
         <v>2500</v>
       </c>
       <c r="D22" s="47">
-        <f>'맛집 상세'!F10</f>
+        <f>'맛집 상세'!F8</f>
         <v>3500</v>
       </c>
       <c r="E22" s="47">
@@ -1215,12 +1217,11 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>카나데 라운지</t>
-        </is>
-      </c>
-      <c r="C28" s="47">
-        <f>'맛집 상세'!E23</f>
-        <v>1600</v>
+          <t>카나데 라운지 (선택 · 상한만)</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="47">
         <f>'맛집 상세'!F23</f>
@@ -1228,7 +1229,7 @@
       </c>
       <c r="E28" s="47">
         <f>C28*$B$17</f>
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="F28" s="47">
         <f>D28*$B$17</f>
@@ -1324,7 +1325,7 @@
       </c>
       <c r="C32" s="48">
         <f>SUM(C19:C31)</f>
-        <v>31600</v>
+        <v>30000</v>
       </c>
       <c r="D32" s="48">
         <f>SUM(D19:D31)</f>
@@ -1332,7 +1333,7 @@
       </c>
       <c r="E32" s="48">
         <f>SUM(E19:E31)</f>
-        <v>94800</v>
+        <v>90000</v>
       </c>
       <c r="F32" s="48">
         <f>SUM(F19:F31)</f>
@@ -1438,7 +1439,7 @@
       </c>
       <c r="C37" s="48">
         <f>C32+C36</f>
-        <v>33400</v>
+        <v>31800</v>
       </c>
       <c r="D37" s="48">
         <f>D32+D36</f>
@@ -1446,7 +1447,7 @@
       </c>
       <c r="E37" s="48">
         <f>E32+E36</f>
-        <v>100200</v>
+        <v>95400</v>
       </c>
       <c r="F37" s="48">
         <f>F32+F36</f>
@@ -1616,7 +1617,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>서부 일정일 14:00</t>
+          <t>선택 (10/2 쇼핑 날)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -1626,12 +1627,12 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>미예약·빈자리 미확인</t>
+          <t>이번 일정에서 빠짐 · 선택</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>기본 10/3, 가마쿠라 날짜 변경 시 10/2. 실제 예약은 별도 변경. 창가 보장 없음.</t>
+          <t>10/2를 쇼핑 날로 바꾸며 뺐음. 좌석을 예약했다면 취소. 쉬어 가고 싶을 때만(에비스에서 JR 한 정거장).</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1750,7 @@
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>원본 맛집 파일과 이전 엑셀은 보존했습니다. 이 10/1 수정안은 웹·캘린더와 같은 기본 동선입니다. 웹에서 가마쿠라 날짜를 바꿔도 이 엑셀은 기본안이므로 14행의 교체 안내를 따르세요.</t>
+          <t>원본 맛집 파일과 이전 엑셀은 보존했습니다. 이 10/2 수정안은 웹·캘린더와 같은 최종 동선입니다.</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2061,7 @@
       <c r="B8" s="32" t="inlineStr">
         <is>
           <t>일정
-10/2 점심</t>
+10/3 점심</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
@@ -2086,7 +2087,7 @@
       <c r="G8" s="15" t="inlineStr">
         <is>
           <t>점심 11:00~15:30 / 목요일 휴무
-예약 불가. 금요일 10:45 도착 목표.</t>
+예약 불가. 토요일 10:45 도착 목표(주말 대기 가능).</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -2188,7 +2189,7 @@
       <c r="B10" s="32" t="inlineStr">
         <is>
           <t>일정
-10/3 점심</t>
+10/2 점심</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
@@ -2202,7 +2203,7 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>히레카츠 또는 로스카츠 정식
-메이지신궁 다음 오모테산도 방향에 있어 음식 때문에 멀리 돌아가지 않아도 됨.</t>
+쇼핑 날 점심. 숙소에서 택시로 약 15분, 이후 택시로 에비스(약 10분).</t>
         </is>
       </c>
       <c r="E10" s="50" t="n">
@@ -2214,7 +2215,7 @@
       <c r="G10" s="15" t="inlineStr">
         <is>
           <t>11:00~22:00 / 주문마감 21:00
-토·일 일반 식사 예약 불가(연회 코스 제외). 10:45 도착, 11:00 식사 목표.</t>
+금요일 11:00 오픈에 맞춰 도착 목표. 토·일 일반 식사 예약 불가(연회 코스 제외).</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -2997,8 +2998,8 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>주 카페
-서부 일정일</t>
+          <t>선택 카페
+쉬어 가고 싶을 때</t>
         </is>
       </c>
       <c r="C23" s="29" t="inlineStr">
@@ -3030,7 +3031,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>기본 10/3 14:00~15:30, 가마쿠라를 10/3으로 바꾸면 10/2 방문. 날짜 변경 시 실제 예약도 별도 변경해야 함. 2시간 이용·10분 무연락 지각 시 취소 안내. 금액은 세금·서비스 15% 포함.</t>
+          <t>10/2를 쇼핑 날로 바꾸며 일정에서 뺐습니다. 에비스에서 JR 한 정거장(메구로)이라 쉬어 가고 싶을 때만. 좌석을 예약했다면 날짜·취소를 확인. 2시간 이용·10분 무연락 지각 시 취소 안내. 금액은 세금·서비스 15% 포함.</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">

--- a/tokyo/tokyo-family-final.xlsx
+++ b/tokyo/tokyo-family-final.xlsx
@@ -3026,7 +3026,7 @@
         <is>
           <t>10:30~22:30 / 주문마감 21:30
 케이크 14:00~17:00
-14:00 좌석만 예약 희망 / 빈자리 미확인</t>
+일정에 없음 · 예약 없이 선택 방문</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
